--- a/tableau_contraintes.xlsx
+++ b/tableau_contraintes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://canope-my.sharepoint.com/personal/hugues_pourageaud_reseau-canope_fr/Documents/Documents/Atelier/Webinaires/Webinaires IA Lecture Jeunesse/tirage_ecriture_contraintes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{401AE3B1-38C7-42AA-8E92-4AD0A2B0880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1738278F-2E82-4041-A1D0-7FE7CABBA63D}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{401AE3B1-38C7-42AA-8E92-4AD0A2B0880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9B945D-19F3-4E9C-A927-BBDFC3EBB642}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{A3D457B3-AF07-49CC-9FF9-0DAF7A9A22DE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A3D457B3-AF07-49CC-9FF9-0DAF7A9A22DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>Une maison en ruine</t>
   </si>
   <si>
-    <t>Une stylo qui écrit avec une encre invisible</t>
+    <t>Un stylo qui écrit avec une encre invisible</t>
   </si>
 </sst>
 </file>
@@ -219,10 +219,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
